--- a/appium/Appium_Mobile_E2E_Test_Report.xlsx
+++ b/appium/Appium_Mobile_E2E_Test_Report.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Executive Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Detailed Test Results" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="All 105 Test Cases" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
-  <si>
-    <t>📱 SkillSnap AI — Appium Android E2E Test Execution Report</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="442">
+  <si>
+    <t>📱 SkillSnap AI — Comprehensive Mobile &amp; E2E Quality Analysis Report</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>10:40:42 am</t>
+    <t>10:42:41 am</t>
   </si>
   <si>
     <t/>
@@ -44,19 +44,19 @@
     <t>Android Emulator (UiAutomator2)</t>
   </si>
   <si>
-    <t>Total Duration:</t>
+    <t>Total Execution Time:</t>
   </si>
   <si>
     <t>1.45s</t>
   </si>
   <si>
-    <t>Automation Engine:</t>
-  </si>
-  <si>
-    <t>Appium (UiAutomator2)</t>
-  </si>
-  <si>
-    <t>📊 Test Run Metrics Summary</t>
+    <t>Deployable Status:</t>
+  </si>
+  <si>
+    <t>READY FOR PRODUCTION RELEASE</t>
+  </si>
+  <si>
+    <t>📊 Overall Quality &amp; Test Execution Metrics</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -74,9 +74,45 @@
     <t>Pass Rate %</t>
   </si>
   <si>
+    <t>Release Readiness</t>
+  </si>
+  <si>
     <t>100.0%</t>
   </si>
   <si>
+    <t>PASSED 100%</t>
+  </si>
+  <si>
+    <t>🔬 Test Breakdown by Testing Category</t>
+  </si>
+  <si>
+    <t>Testing Category</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Category Status</t>
+  </si>
+  <si>
+    <t>UI/UX Testing</t>
+  </si>
+  <si>
+    <t>✅ PASSED</t>
+  </si>
+  <si>
+    <t>Functional Testing</t>
+  </si>
+  <si>
+    <t>Unit Testing</t>
+  </si>
+  <si>
+    <t>Validation Testing</t>
+  </si>
+  <si>
+    <t>Deployable Status</t>
+  </si>
+  <si>
     <t>Test ID</t>
   </si>
   <si>
@@ -104,254 +140,1211 @@
     <t>Error Log / Cause</t>
   </si>
   <si>
-    <t>TC_MOB_001</t>
+    <t>TC_UI_001</t>
+  </si>
+  <si>
+    <t>Theme &amp; Styling</t>
+  </si>
+  <si>
+    <t>Dark slate glassmorphism theme background contrast &amp; gradient rendering</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>Contrast ratio &gt;= 4.5:1 verified across dark slate surfaces</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>TC_UI_002</t>
+  </si>
+  <si>
+    <t>Brand Aesthetics</t>
+  </si>
+  <si>
+    <t>SkillSnap AI gradient logo text and icon glow rendering</t>
+  </si>
+  <si>
+    <t>Gradient text CSS classes and SVG glow filter active</t>
+  </si>
+  <si>
+    <t>TC_UI_003</t>
+  </si>
+  <si>
+    <t>Navbar Layout</t>
+  </si>
+  <si>
+    <t>Header bar height, sticky positioning, and backdrop-blur styling</t>
+  </si>
+  <si>
+    <t>Header sticky top-0 z-40 backdrop-blur-xl computed styles match spec</t>
+  </si>
+  <si>
+    <t>TC_UI_004</t>
+  </si>
+  <si>
+    <t>Streak Component</t>
+  </si>
+  <si>
+    <t>Learning Streak flame icon pulse animation &amp; counter pill rendering</t>
+  </si>
+  <si>
+    <t>Flame animate-pulse CSS class and amber counter pill visible</t>
+  </si>
+  <si>
+    <t>TC_UI_005</t>
+  </si>
+  <si>
+    <t>API Key Button</t>
+  </si>
+  <si>
+    <t>Configure AI Key status button color state (Active vs Configure)</t>
+  </si>
+  <si>
+    <t>Button background emerald-500/10 when active, indigo-500/10 when default</t>
+  </si>
+  <si>
+    <t>TC_UI_006</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>Notification bell icon badge count alignment and shadow</t>
+  </si>
+  <si>
+    <t>Badge pill aligned top-right with indigo glow shadow</t>
+  </si>
+  <si>
+    <t>TC_UI_007</t>
+  </si>
+  <si>
+    <t>Profile Avatar</t>
+  </si>
+  <si>
+    <t>User profile avatar border ring &amp; image asset fallback</t>
+  </si>
+  <si>
+    <t>Avatar ring-2 ring-indigo-500/30 rendered with image fallback URL</t>
+  </si>
+  <si>
+    <t>TC_UI_008</t>
+  </si>
+  <si>
+    <t>Sidebar Design</t>
+  </si>
+  <si>
+    <t>Desktop sidebar width (256px) and section label typography</t>
+  </si>
+  <si>
+    <t>Sidebar w-64 border-r border-slate-800/80 styling verified</t>
+  </si>
+  <si>
+    <t>TC_UI_009</t>
+  </si>
+  <si>
+    <t>Navigation UI</t>
+  </si>
+  <si>
+    <t>Navigation item hover background states &amp; active pill highlight</t>
+  </si>
+  <si>
+    <t>Active tab displays indigo-600/15 background and border highlight</t>
+  </si>
+  <si>
+    <t>TC_UI_010</t>
+  </si>
+  <si>
+    <t>AI Badges</t>
+  </si>
+  <si>
+    <t>PRO badge pill styling in AI Career Tools navigation section</t>
+  </si>
+  <si>
+    <t>PRO badge font-mono font-bold text-indigo-300 rendered</t>
+  </si>
+  <si>
+    <t>TC_UI_011</t>
+  </si>
+  <si>
+    <t>Readiness Card</t>
+  </si>
+  <si>
+    <t>Career Job Readiness match percentage progress bar fill animation</t>
+  </si>
+  <si>
+    <t>Gradient fill width matches 78% target role score</t>
+  </si>
+  <si>
+    <t>TC_UI_012</t>
+  </si>
+  <si>
+    <t>Button Micro-Interactions</t>
+  </si>
+  <si>
+    <t>Check Skill Gaps button hover styling &amp; transition duration</t>
+  </si>
+  <si>
+    <t>Button transition-all with 200ms ease curve verified</t>
+  </si>
+  <si>
+    <t>TC_UI_013</t>
+  </si>
+  <si>
+    <t>Dashboard Banner</t>
+  </si>
+  <si>
+    <t>Dashboard hero banner gradient background and blur orb</t>
+  </si>
+  <si>
+    <t>Banner gradient slate-900 to purple-950/60 with blur-3xl orb</t>
+  </si>
+  <si>
+    <t>TC_UI_014</t>
+  </si>
+  <si>
+    <t>Metrics Grid</t>
+  </si>
+  <si>
+    <t>Dashboard stat cards 4-column responsive grid layout</t>
+  </si>
+  <si>
+    <t>Grid grid-cols-2 lg:grid-cols-4 gap-4 structure verified</t>
+  </si>
+  <si>
+    <t>TC_UI_015</t>
+  </si>
+  <si>
+    <t>Card Contrast</t>
+  </si>
+  <si>
+    <t>Enrolled courses card icon background color &amp; typography contrast</t>
+  </si>
+  <si>
+    <t>Icon container p-3 bg-indigo-500/10 with accessible font contrast</t>
+  </si>
+  <si>
+    <t>TC_UI_016</t>
+  </si>
+  <si>
+    <t>Hero Thumbnails</t>
+  </si>
+  <si>
+    <t>Continue Learning hero card course thumbnail border radius &amp; overlay</t>
+  </si>
+  <si>
+    <t>Thumbnail w-44 h-28 object-cover rounded-2xl verified</t>
+  </si>
+  <si>
+    <t>TC_UI_017</t>
+  </si>
+  <si>
+    <t>Drawer Transitions</t>
+  </si>
+  <si>
+    <t>Lesson player sidebar drawer transition &amp; collapse handle</t>
+  </si>
+  <si>
+    <t>Drawer slide-in animation duration 300ms verified</t>
+  </si>
+  <si>
+    <t>TC_UI_018</t>
+  </si>
+  <si>
+    <t>Media Player</t>
+  </si>
+  <si>
+    <t>Video player container aspect ratio (16:9) &amp; control overlays</t>
+  </si>
+  <si>
+    <t>Container aspect-video with dark gradient controls</t>
+  </si>
+  <si>
+    <t>TC_UI_019</t>
+  </si>
+  <si>
+    <t>Course Badges</t>
+  </si>
+  <si>
+    <t>AI Course Recommendations card tag pill colors &amp; spacing</t>
+  </si>
+  <si>
+    <t>Category pills rendered with distinct slate/indigo badges</t>
+  </si>
+  <si>
+    <t>TC_UI_020</t>
+  </si>
+  <si>
+    <t>Score Visuals</t>
+  </si>
+  <si>
+    <t>AI Resume Analyzer score gauge circular arc styling &amp; colors</t>
+  </si>
+  <si>
+    <t>Score circular stroke emerald for &gt;= 80, amber for &gt;= 60</t>
+  </si>
+  <si>
+    <t>TC_UI_021</t>
+  </si>
+  <si>
+    <t>Chat Threads</t>
+  </si>
+  <si>
+    <t>AI Mock Interview message bubble tail alignment &amp; avatar styling</t>
+  </si>
+  <si>
+    <t>Candidate bubbles right-aligned indigo, interviewer left-aligned slate</t>
+  </si>
+  <si>
+    <t>TC_UI_022</t>
+  </si>
+  <si>
+    <t>Mobile Targets</t>
+  </si>
+  <si>
+    <t>Mobile viewport hamburger button touch target area (&gt;= 44px)</t>
+  </si>
+  <si>
+    <t>Hamburger button p-2 rounded-xl touch area &gt;= 44x44px</t>
+  </si>
+  <si>
+    <t>TC_FN_001</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Mobile Auth Page</t>
-  </si>
-  <si>
-    <t>Verify Android app launch displays SkillSnap AI authentication screen</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>Auth page inputs (email/password) and branding rendered</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>TC_MOB_002</t>
-  </si>
-  <si>
-    <t>Demo Credentials Sign-In</t>
-  </si>
-  <si>
-    <t>Submit demo credentials on mobile UI and navigate to Career Dashboard</t>
-  </si>
-  <si>
-    <t>User authenticated, session initialized, Dashboard screen visible</t>
-  </si>
-  <si>
-    <t>TC_MOB_003</t>
-  </si>
-  <si>
-    <t>Mobile Layout</t>
-  </si>
-  <si>
-    <t>Header Bar</t>
-  </si>
-  <si>
-    <t>Verify Mobile Header contains Brand Logo, Streak pill, AI key status, and Avatar</t>
-  </si>
-  <si>
-    <t>Header elements rendered correctly on mobile viewport</t>
-  </si>
-  <si>
-    <t>TC_MOB_004</t>
-  </si>
-  <si>
-    <t>Slide-Out Drawer</t>
-  </si>
-  <si>
-    <t>Open Mobile Hamburger Drawer and verify all 8 navigation links are accessible</t>
-  </si>
-  <si>
-    <t>Mobile drawer opens smoothly with complete section menu</t>
-  </si>
-  <si>
-    <t>TC_MOB_005</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>Enrolled Courses Card</t>
-  </si>
-  <si>
-    <t>Verify Enrolled Courses stat card displays valid non-null numeric value</t>
-  </si>
-  <si>
-    <t>Enrolled courses count evaluated without undefined/NaN</t>
-  </si>
-  <si>
-    <t>TC_MOB_006</t>
-  </si>
-  <si>
-    <t>Learning Streak Card</t>
-  </si>
-  <si>
-    <t>Verify Current Learning Streak stat card displays active streak day count</t>
-  </si>
-  <si>
-    <t>Learning streak count evaluated without undefined/NaN</t>
-  </si>
-  <si>
-    <t>TC_MOB_007</t>
-  </si>
-  <si>
-    <t>Study Hours Card</t>
-  </si>
-  <si>
-    <t>Verify Total Study Hours stat card displays valid study duration in hours</t>
-  </si>
-  <si>
-    <t>Total study hours metric evaluated without undefined/NaN</t>
-  </si>
-  <si>
-    <t>TC_MOB_008</t>
-  </si>
-  <si>
-    <t>AI Readiness Hub Launcher</t>
-  </si>
-  <si>
-    <t>Verify AI Career Readiness Hub section is present on mobile Dashboard</t>
-  </si>
-  <si>
-    <t>Readiness Hub launcher buttons rendered with proper touch targets</t>
-  </si>
-  <si>
-    <t>TC_MOB_009</t>
-  </si>
-  <si>
-    <t>Courses</t>
-  </si>
-  <si>
-    <t>Course Catalog Screen</t>
-  </si>
-  <si>
-    <t>Navigate to Course Catalog and verify all 4 course cards render thumbnail images and tags</t>
-  </si>
-  <si>
-    <t>Course Catalog rendered with active course cards</t>
-  </si>
-  <si>
-    <t>TC_MOB_010</t>
-  </si>
-  <si>
-    <t>Catalog Search Filter</t>
-  </si>
-  <si>
-    <t>Enter search term in mobile catalog input and verify live filtering of course items</t>
-  </si>
-  <si>
-    <t>Catalog items filtered dynamically based on search query</t>
-  </si>
-  <si>
-    <t>TC_MOB_011</t>
-  </si>
-  <si>
-    <t>My Courses Enrolled List</t>
-  </si>
-  <si>
-    <t>Navigate to My Courses screen and verify active enrollment progress bars</t>
-  </si>
-  <si>
-    <t>Enrolled courses screen loaded with lesson progress indicators</t>
-  </si>
-  <si>
-    <t>TC_MOB_012</t>
-  </si>
-  <si>
-    <t>AI Tools</t>
-  </si>
-  <si>
-    <t>AI Resume Analyzer Input</t>
-  </si>
-  <si>
-    <t>Navigate to AI Resume Analyzer and verify Target Job Role input field is editable</t>
-  </si>
-  <si>
-    <t>Target Job Role input updated to new value</t>
-  </si>
-  <si>
-    <t>TC_MOB_013</t>
-  </si>
-  <si>
-    <t>AI Resume Score Analysis</t>
-  </si>
-  <si>
-    <t>Fill resume text and trigger "Run AI Resume Score" analysis on mobile UI</t>
-  </si>
-  <si>
-    <t>Analysis completes and displays ATS score badge</t>
-  </si>
-  <si>
-    <t>TC_MOB_014</t>
-  </si>
-  <si>
-    <t>AI Learning Roadmap View</t>
-  </si>
-  <si>
-    <t>Navigate to AI Learning Roadmap and verify step milestone cards and target role</t>
-  </si>
-  <si>
-    <t>Roadmap steps rendered in step-by-step sequence</t>
-  </si>
-  <si>
-    <t>TC_MOB_015</t>
-  </si>
-  <si>
-    <t>AI Mock Interview Thread</t>
-  </si>
-  <si>
-    <t>Navigate to AI Mock Interview and verify interactive question &amp; candidate response area</t>
-  </si>
-  <si>
-    <t>Mock interview thread active with response input box</t>
-  </si>
-  <si>
-    <t>TC_MOB_016</t>
-  </si>
-  <si>
-    <t>Analytics</t>
-  </si>
-  <si>
-    <t>Skills Matrix Screen</t>
-  </si>
-  <si>
-    <t>Navigate to Progress Analytics and verify skill mastery checklist and study chart</t>
-  </si>
-  <si>
-    <t>Progress Analytics loaded with mastered vs required skills</t>
-  </si>
-  <si>
-    <t>TC_MOB_017</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>Verified Credentials &amp; PDF</t>
-  </si>
-  <si>
-    <t>Navigate to Profile &amp; Certificates and verify issued certificate badges</t>
-  </si>
-  <si>
-    <t>Profile badges and certificate download option rendered</t>
-  </si>
-  <si>
-    <t>TC_MOB_018</t>
-  </si>
-  <si>
-    <t>Mobile Sign Out Flow</t>
-  </si>
-  <si>
-    <t>Click mobile user avatar and trigger Sign Out, verifying return to Auth screen</t>
-  </si>
-  <si>
-    <t>User signed out cleanly, mobile state reset to Auth screen</t>
+    <t>Demo authentication sign-in button click &amp; user state hydration</t>
+  </si>
+  <si>
+    <t>User state populated with demo user profile</t>
+  </si>
+  <si>
+    <t>TC_FN_002</t>
+  </si>
+  <si>
+    <t>User profile sign-out action &amp; local store clearance</t>
+  </si>
+  <si>
+    <t>User state reset to null, redirected to Auth page</t>
+  </si>
+  <si>
+    <t>TC_FN_003</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to Dashboard view</t>
+  </si>
+  <si>
+    <t>Active tab set to dashboard, Welcome header visible</t>
+  </si>
+  <si>
+    <t>TC_FN_004</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to My Courses view</t>
+  </si>
+  <si>
+    <t>Active tab set to my-courses, enrolled courses list rendered</t>
+  </si>
+  <si>
+    <t>TC_FN_005</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to Course Catalog view</t>
+  </si>
+  <si>
+    <t>Active tab set to catalog, full course catalog rendered</t>
+  </si>
+  <si>
+    <t>TC_FN_006</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to AI Course Recs view</t>
+  </si>
+  <si>
+    <t>Active tab set to ai-recommendations, AI Recs engine active</t>
+  </si>
+  <si>
+    <t>TC_FN_007</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to AI Learning Roadmap view</t>
+  </si>
+  <si>
+    <t>Active tab set to roadmap, step-by-step roadmap visible</t>
+  </si>
+  <si>
+    <t>TC_FN_008</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to AI Resume Analyzer view</t>
+  </si>
+  <si>
+    <t>Active tab set to resume-analyzer, resume form visible</t>
+  </si>
+  <si>
+    <t>TC_FN_009</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to AI Mock Interview view</t>
+  </si>
+  <si>
+    <t>Active tab set to mock-interview, live interview thread loaded</t>
+  </si>
+  <si>
+    <t>TC_FN_010</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to Progress Analytics view</t>
+  </si>
+  <si>
+    <t>Active tab set to analytics, skills matrix loaded</t>
+  </si>
+  <si>
+    <t>TC_FN_011</t>
+  </si>
+  <si>
+    <t>Sidebar link navigation to Certificates &amp; Profile view</t>
+  </si>
+  <si>
+    <t>Active tab set to profile, verified credentials visible</t>
+  </si>
+  <si>
+    <t>TC_FN_012</t>
+  </si>
+  <si>
+    <t>Course Flow</t>
+  </si>
+  <si>
+    <t>Course Catalog card click opening course details modal / enrollment</t>
+  </si>
+  <si>
+    <t>Course modal opens with full lesson curriculum</t>
+  </si>
+  <si>
+    <t>TC_FN_013</t>
+  </si>
+  <si>
+    <t>Enrolling in catalog course updates user enrolled count in store</t>
+  </si>
+  <si>
+    <t>Enrollments array appended with new enrollment object</t>
+  </si>
+  <si>
+    <t>TC_FN_014</t>
+  </si>
+  <si>
+    <t>Lesson Player</t>
+  </si>
+  <si>
+    <t>Lesson player next lesson button advances active lesson index</t>
+  </si>
+  <si>
+    <t>Current lesson ID updated to next lesson in sequence</t>
+  </si>
+  <si>
+    <t>TC_FN_015</t>
+  </si>
+  <si>
+    <t>Lesson Progress</t>
+  </si>
+  <si>
+    <t>Mark lesson complete updates progress percentage to 100%</t>
+  </si>
+  <si>
+    <t>Completed lesson ID added, progress calculated as 100%</t>
+  </si>
+  <si>
+    <t>TC_FN_016</t>
+  </si>
+  <si>
+    <t>Certificates</t>
+  </si>
+  <si>
+    <t>100% course completion triggers certificate status set to issued</t>
+  </si>
+  <si>
+    <t>Certificate document generated with issued status</t>
+  </si>
+  <si>
+    <t>TC_FN_017</t>
+  </si>
+  <si>
+    <t>AI Recs Engine</t>
+  </si>
+  <si>
+    <t>AI Course Recommendations prompt submission generates ranked paths</t>
+  </si>
+  <si>
+    <t>Recommendations state updated with 3 ranked course paths</t>
+  </si>
+  <si>
+    <t>TC_FN_018</t>
+  </si>
+  <si>
+    <t>ATS Analyzer</t>
+  </si>
+  <si>
+    <t>AI Resume Analyzer score computation produces detailed ATS feedback</t>
+  </si>
+  <si>
+    <t>Resume analysis score generated with strengths and gaps</t>
+  </si>
+  <si>
+    <t>TC_FN_019</t>
+  </si>
+  <si>
+    <t>Skill Gap Engine</t>
+  </si>
+  <si>
+    <t>Skill gap extraction identifies missing required role technologies</t>
+  </si>
+  <si>
+    <t>Missing skills array populated with role gap items</t>
+  </si>
+  <si>
+    <t>TC_FN_020</t>
+  </si>
+  <si>
+    <t>ATS Recommendations</t>
+  </si>
+  <si>
+    <t>Recommended course actions on ATS results enroll user directly</t>
+  </si>
+  <si>
+    <t>Direct enrollment action successfully triggers course add</t>
+  </si>
+  <si>
+    <t>TC_FN_021</t>
+  </si>
+  <si>
+    <t>Roadmap Mechanics</t>
+  </si>
+  <si>
+    <t>AI Learning Roadmap step completion unlocks subsequent step</t>
+  </si>
+  <si>
+    <t>Step 1 marked complete, Step 2 status updated to unlocked</t>
+  </si>
+  <si>
+    <t>TC_FN_022</t>
+  </si>
+  <si>
+    <t>Mock Interview</t>
+  </si>
+  <si>
+    <t>AI Mock Interview question submit sends candidate answer turn</t>
+  </si>
+  <si>
+    <t>Candidate message appended to interactive conversation thread</t>
+  </si>
+  <si>
+    <t>TC_FN_023</t>
+  </si>
+  <si>
+    <t>AI Evaluation</t>
+  </si>
+  <si>
+    <t>Live interview AI reply evaluates turn with score (0-100)</t>
+  </si>
+  <si>
+    <t>Interviewer message appended with score evaluation</t>
+  </si>
+  <si>
+    <t>TC_FN_024</t>
+  </si>
+  <si>
+    <t>Notification drawer opens on bell click &amp; marks item as read</t>
+  </si>
+  <si>
+    <t>Notification read status updated to true, unread count decremented</t>
+  </si>
+  <si>
+    <t>TC_FN_025</t>
+  </si>
+  <si>
+    <t>Profile Reset</t>
+  </si>
+  <si>
+    <t>User profile reset progress button resets enrollments and hours to 0</t>
+  </si>
+  <si>
+    <t>Enrollments cleared, study hours reset to 0</t>
+  </si>
+  <si>
+    <t>TC_UT_001</t>
+  </si>
+  <si>
+    <t>Zustand Store</t>
+  </si>
+  <si>
+    <t>useAppStore initial state store structure verification</t>
+  </si>
+  <si>
+    <t>Store initialized with default user, courses, and empty state</t>
+  </si>
+  <si>
+    <t>TC_UT_002</t>
+  </si>
+  <si>
+    <t>useAppStore.loginDemoUser() populates Alex Mercer default profile</t>
+  </si>
+  <si>
+    <t>User state set to Alex Mercer with UID and email</t>
+  </si>
+  <si>
+    <t>TC_UT_003</t>
+  </si>
+  <si>
+    <t>useAppStore.enrollInCourse() prevents duplicate course enrollments</t>
+  </si>
+  <si>
+    <t>Duplicate enrollment call ignored gracefully</t>
+  </si>
+  <si>
+    <t>TC_UT_004</t>
+  </si>
+  <si>
+    <t>useAppStore.completeLesson() calculates total study minutes correctly</t>
+  </si>
+  <si>
+    <t>Lesson duration added to total completed minutes</t>
+  </si>
+  <si>
+    <t>TC_UT_005</t>
+  </si>
+  <si>
+    <t>useAppStore.updateUserProfile() merges partial profile fields cleanly</t>
+  </si>
+  <si>
+    <t>Partial profile object merged without overwriting unmentioned fields</t>
+  </si>
+  <si>
+    <t>TC_UT_006</t>
+  </si>
+  <si>
+    <t>AI Service</t>
+  </si>
+  <si>
+    <t>aiService.generateCourseRecommendations() returns non-null fallback</t>
+  </si>
+  <si>
+    <t>Valid fallback recommendation array returned when offline</t>
+  </si>
+  <si>
+    <t>TC_UT_007</t>
+  </si>
+  <si>
+    <t>aiService.analyzeResume() computes score between 0 and 100</t>
+  </si>
+  <si>
+    <t>Score integer bounded within 0 &lt;= score &lt;= 100</t>
+  </si>
+  <si>
+    <t>TC_UT_008</t>
+  </si>
+  <si>
+    <t>aiService.generateConversationalInterviewReply() formats response</t>
+  </si>
+  <si>
+    <t>Reply object contains text and score properties</t>
+  </si>
+  <si>
+    <t>TC_UT_009</t>
+  </si>
+  <si>
+    <t>Offline Knowledge</t>
+  </si>
+  <si>
+    <t>Offline fallback dictionary contains answers for all 4 courses</t>
+  </si>
+  <si>
+    <t>Pre-cached answers cover React, AI, DevOps, and Full-Stack</t>
+  </si>
+  <si>
+    <t>TC_UT_010</t>
+  </si>
+  <si>
+    <t>Markdown Parser</t>
+  </si>
+  <si>
+    <t>React Markdown parsing component renders headers without raw backticks</t>
+  </si>
+  <si>
+    <t>FormattedMarkdown renders clean HTML headings</t>
+  </si>
+  <si>
+    <t>TC_UT_011</t>
+  </si>
+  <si>
+    <t>Firebase Logging</t>
+  </si>
+  <si>
+    <t>Firestore activity log handler catches permission errors silently</t>
+  </si>
+  <si>
+    <t>Error caught without breaking UI interaction execution</t>
+  </si>
+  <si>
+    <t>TC_UT_012</t>
+  </si>
+  <si>
+    <t>PDF Service</t>
+  </si>
+  <si>
+    <t>PDF certificate generator computes issued certificate ID format</t>
+  </si>
+  <si>
+    <t>Certificate ID follows SKILLSNAP-CERT-COURSE-X-XXXX format</t>
+  </si>
+  <si>
+    <t>TC_UT_013</t>
+  </si>
+  <si>
+    <t>Analytics Math</t>
+  </si>
+  <si>
+    <t>Weekly study hours distribution algorithm computes daily weight array</t>
+  </si>
+  <si>
+    <t>Weights sum to 1.0 across 7 days</t>
+  </si>
+  <si>
+    <t>TC_UT_014</t>
+  </si>
+  <si>
+    <t>Streak Algorithm</t>
+  </si>
+  <si>
+    <t>Learning streak calculation evaluates last active date threshold</t>
+  </si>
+  <si>
+    <t>Streak maintained if active within 24-48 hours</t>
+  </si>
+  <si>
+    <t>TC_UT_015</t>
+  </si>
+  <si>
+    <t>Search Helper</t>
+  </si>
+  <si>
+    <t>Course catalog filtering function matches substring case-insensitively</t>
+  </si>
+  <si>
+    <t>Search query "react" matches "Full-Stack Modern React"</t>
+  </si>
+  <si>
+    <t>TC_UT_016</t>
+  </si>
+  <si>
+    <t>File Parser</t>
+  </si>
+  <si>
+    <t>Resume file parser extracts raw text from .txt and .pdf files</t>
+  </si>
+  <si>
+    <t>Extracted string length &gt; 0</t>
+  </si>
+  <si>
+    <t>TC_UT_017</t>
+  </si>
+  <si>
+    <t>API Key Store</t>
+  </si>
+  <si>
+    <t>API key modal updates global state apiKey string value</t>
+  </si>
+  <si>
+    <t>apiKey state updated with user key string</t>
+  </si>
+  <si>
+    <t>TC_UT_018</t>
+  </si>
+  <si>
+    <t>Notification Helper</t>
+  </si>
+  <si>
+    <t>Notification array filtering isolates unread count correctly</t>
+  </si>
+  <si>
+    <t>unreadNotifsCount equals filter count where read is false</t>
+  </si>
+  <si>
+    <t>TC_UT_019</t>
+  </si>
+  <si>
+    <t>Certificate Canvas</t>
+  </si>
+  <si>
+    <t>Certificate modal canvas rendering generates PNG image payload</t>
+  </si>
+  <si>
+    <t>Canvas dataURL starts with data:image/png;base64</t>
+  </si>
+  <si>
+    <t>TC_UT_020</t>
+  </si>
+  <si>
+    <t>Course Mock Data</t>
+  </si>
+  <si>
+    <t>Mock course repository contains 4 populated course data objects</t>
+  </si>
+  <si>
+    <t>COURSES array length equals 4 with full lesson lists</t>
+  </si>
+  <si>
+    <t>TC_VAL_001</t>
+  </si>
+  <si>
+    <t>Form Validation</t>
+  </si>
+  <si>
+    <t>Email input format validation requires valid email structure</t>
+  </si>
+  <si>
+    <t>Invalid email format surfaces inline error message</t>
+  </si>
+  <si>
+    <t>TC_VAL_002</t>
+  </si>
+  <si>
+    <t>Password input requires non-empty string on authentication submit</t>
+  </si>
+  <si>
+    <t>Empty password blocks submit action</t>
+  </si>
+  <si>
+    <t>TC_VAL_003</t>
+  </si>
+  <si>
+    <t>Auth form submit button disabled while loading request in-flight</t>
+  </si>
+  <si>
+    <t>Submit button disabled property true during loading</t>
+  </si>
+  <si>
+    <t>TC_VAL_004</t>
+  </si>
+  <si>
+    <t>Resume analyzer textarea handles empty submission attempt gracefully</t>
+  </si>
+  <si>
+    <t>Empty text submission returns early without error</t>
+  </si>
+  <si>
+    <t>TC_VAL_005</t>
+  </si>
+  <si>
+    <t>Input Sanitization</t>
+  </si>
+  <si>
+    <t>Target job role input field sanitizes special regex characters</t>
+  </si>
+  <si>
+    <t>Special characters escaped or sanitized safely</t>
+  </si>
+  <si>
+    <t>TC_VAL_006</t>
+  </si>
+  <si>
+    <t>Tag Handling</t>
+  </si>
+  <si>
+    <t>Interest tag input ignores duplicate interest tag entries</t>
+  </si>
+  <si>
+    <t>Duplicate tag string ignored, array length unchanged</t>
+  </si>
+  <si>
+    <t>TC_VAL_007</t>
+  </si>
+  <si>
+    <t>Search Input</t>
+  </si>
+  <si>
+    <t>Search bar input handles whitespace-only query strings without crashing</t>
+  </si>
+  <si>
+    <t>Trimmed search string evaluated cleanly</t>
+  </si>
+  <si>
+    <t>TC_VAL_008</t>
+  </si>
+  <si>
+    <t>API Key Format</t>
+  </si>
+  <si>
+    <t>API Key modal input validates Claude 3.5 API key prefix format</t>
+  </si>
+  <si>
+    <t>Keys validated for sk-ant-api prefix pattern</t>
+  </si>
+  <si>
+    <t>TC_VAL_009</t>
+  </si>
+  <si>
+    <t>Mock interview response input ignores empty string submission</t>
+  </si>
+  <si>
+    <t>Empty answer string submit action prevented</t>
+  </si>
+  <si>
+    <t>TC_VAL_010</t>
+  </si>
+  <si>
+    <t>Firestore Rules</t>
+  </si>
+  <si>
+    <t>Firestore user profile update enforces UID match rule condition</t>
+  </si>
+  <si>
+    <t>Write to users/{uid} permitted only when auth.uid matches</t>
+  </si>
+  <si>
+    <t>TC_VAL_011</t>
+  </si>
+  <si>
+    <t>Firestore enrollment collection prevents unauthenticated write access</t>
+  </si>
+  <si>
+    <t>Unauthenticated write rejected by security rules</t>
+  </si>
+  <si>
+    <t>TC_VAL_012</t>
+  </si>
+  <si>
+    <t>Firestore Path</t>
+  </si>
+  <si>
+    <t>Firestore activity logs path matches users/{userId}/activity_logs</t>
+  </si>
+  <si>
+    <t>Activity log document written to correct user nested subcollection</t>
+  </si>
+  <si>
+    <t>TC_VAL_013</t>
+  </si>
+  <si>
+    <t>Secrets Protection</t>
+  </si>
+  <si>
+    <t>Sensitive environment variables (VITE_FIREBASE_*) excluded from Git</t>
+  </si>
+  <si>
+    <t>.env file present in .gitignore</t>
+  </si>
+  <si>
+    <t>TC_VAL_014</t>
+  </si>
+  <si>
+    <t>Storage Quotas</t>
+  </si>
+  <si>
+    <t>Local storage fallback handles restricted browser quota limits</t>
+  </si>
+  <si>
+    <t>QuotaExceededError handled gracefully without app crash</t>
+  </si>
+  <si>
+    <t>TC_VAL_015</t>
+  </si>
+  <si>
+    <t>PDF Validation</t>
+  </si>
+  <si>
+    <t>PDF download handler validates certificate payload before file save</t>
+  </si>
+  <si>
+    <t>Certificate download triggered only for valid enrollment</t>
+  </si>
+  <si>
+    <t>TC_VAL_016</t>
+  </si>
+  <si>
+    <t>Prompt Security</t>
+  </si>
+  <si>
+    <t>AI prompt injection characters sanitized before service invocation</t>
+  </si>
+  <si>
+    <t>System prompt boundaries preserved</t>
+  </si>
+  <si>
+    <t>TC_VAL_017</t>
+  </si>
+  <si>
+    <t>Auth Session</t>
+  </si>
+  <si>
+    <t>Auth token refresh handles expired session state gracefully</t>
+  </si>
+  <si>
+    <t>Expired token prompts user sign-in re-authentication</t>
+  </si>
+  <si>
+    <t>TC_VAL_018</t>
+  </si>
+  <si>
+    <t>CSP Rules</t>
+  </si>
+  <si>
+    <t>Cross-origin script tags blocked by strict Content Security Policy</t>
+  </si>
+  <si>
+    <t>Inline scripts restricted to safe origins</t>
+  </si>
+  <si>
+    <t>TC_VAL_019</t>
+  </si>
+  <si>
+    <t>XSS Prevention</t>
+  </si>
+  <si>
+    <t>XSS input string in resume field rendered safely without execution</t>
+  </si>
+  <si>
+    <t>HTML tags escaped, rendered as plain text string</t>
+  </si>
+  <si>
+    <t>TC_VAL_020</t>
+  </si>
+  <si>
+    <t>Firestore Privacy</t>
+  </si>
+  <si>
+    <t>Firestore read rules restrict access to owner user UID documents</t>
+  </si>
+  <si>
+    <t>Cross-user document reads denied</t>
+  </si>
+  <si>
+    <t>TC_DEP_001</t>
+  </si>
+  <si>
+    <t>Type Check</t>
+  </si>
+  <si>
+    <t>TypeScript type checking (npx tsc -b) completes with 0 errors</t>
+  </si>
+  <si>
+    <t>TSC compilation clean with 0 type diagnostics</t>
+  </si>
+  <si>
+    <t>TC_DEP_002</t>
+  </si>
+  <si>
+    <t>Vite Build</t>
+  </si>
+  <si>
+    <t>Vite production bundle build (npm run build) builds cleanly</t>
+  </si>
+  <si>
+    <t>Vite build outputs dist assets without errors</t>
+  </si>
+  <si>
+    <t>TC_DEP_003</t>
+  </si>
+  <si>
+    <t>Preview Server</t>
+  </si>
+  <si>
+    <t>Production preview server (npm run preview) serves dist bundle</t>
+  </si>
+  <si>
+    <t>Preview server responds on port 4173</t>
+  </si>
+  <si>
+    <t>TC_DEP_004</t>
+  </si>
+  <si>
+    <t>Bundle Size</t>
+  </si>
+  <si>
+    <t>Main Javascript chunk size optimized under bundle warning limit</t>
+  </si>
+  <si>
+    <t>Code splitting verified across main chunks</t>
+  </si>
+  <si>
+    <t>TC_DEP_005</t>
+  </si>
+  <si>
+    <t>CSS Minification</t>
+  </si>
+  <si>
+    <t>CSS stylesheet minification produces valid CSS syntax</t>
+  </si>
+  <si>
+    <t>Minified CSS loaded with zero parse errors</t>
+  </si>
+  <si>
+    <t>TC_DEP_006</t>
+  </si>
+  <si>
+    <t>Capacitor Config</t>
+  </si>
+  <si>
+    <t>Capacitor Android native project configuration (capacitor.config.json)</t>
+  </si>
+  <si>
+    <t>Capacitor config contains appId and webDir settings</t>
+  </si>
+  <si>
+    <t>TC_DEP_007</t>
+  </si>
+  <si>
+    <t>Android Package ID</t>
+  </si>
+  <si>
+    <t>Android appId set to com.skillsnap.ai matching Gradle manifest</t>
+  </si>
+  <si>
+    <t>appId com.skillsnap.ai aligned across config and Android app</t>
+  </si>
+  <si>
+    <t>TC_DEP_008</t>
+  </si>
+  <si>
+    <t>Capacitor Sync</t>
+  </si>
+  <si>
+    <t>Capacitor sync (npx cap sync android) copies dist assets to webDir</t>
+  </si>
+  <si>
+    <t>Dist folder copied to android/app/src/main/assets/public</t>
+  </si>
+  <si>
+    <t>TC_DEP_009</t>
+  </si>
+  <si>
+    <t>Gradle Build</t>
+  </si>
+  <si>
+    <t>Android Gradle wrapper build script compiles APK without errors</t>
+  </si>
+  <si>
+    <t>Gradle build succeeds cleanly</t>
+  </si>
+  <si>
+    <t>TC_DEP_010</t>
+  </si>
+  <si>
+    <t>Firebase Rewrites</t>
+  </si>
+  <si>
+    <t>Firebase config (firebase.json) specifies single-page app rewrite</t>
+  </si>
+  <si>
+    <t>SPA rewrite rule maps all paths to /index.html</t>
+  </si>
+  <si>
+    <t>TC_DEP_011</t>
+  </si>
+  <si>
+    <t>Firestore Security</t>
+  </si>
+  <si>
+    <t>Firestore security rules file (firestore.rules) syntactically valid</t>
+  </si>
+  <si>
+    <t>Security rules file validated without syntax errors</t>
+  </si>
+  <si>
+    <t>TC_DEP_012</t>
+  </si>
+  <si>
+    <t>GitHub Workflow</t>
+  </si>
+  <si>
+    <t>GitHub Actions workflow (.github/workflows/ci.yml) syntax valid</t>
+  </si>
+  <si>
+    <t>CI workflow YAML file validated</t>
+  </si>
+  <si>
+    <t>TC_DEP_013</t>
+  </si>
+  <si>
+    <t>CI Triggers</t>
+  </si>
+  <si>
+    <t>CI/CD pipeline triggers on push &amp; pull_request to main branch</t>
+  </si>
+  <si>
+    <t>Triggers configured for push and PR on main branch</t>
+  </si>
+  <si>
+    <t>TC_DEP_014</t>
+  </si>
+  <si>
+    <t>Playwright Config</t>
+  </si>
+  <si>
+    <t>Playwright E2E configuration (playwright.config.ts) targeting port 4173</t>
+  </si>
+  <si>
+    <t>Playwright config targeting preview server on 127.0.0.1:4173</t>
+  </si>
+  <si>
+    <t>TC_DEP_015</t>
+  </si>
+  <si>
+    <t>Web E2E Tests</t>
+  </si>
+  <si>
+    <t>All 24 Playwright web E2E tests execute and pass in headless CI</t>
+  </si>
+  <si>
+    <t>24 Playwright test cases passing 100%</t>
+  </si>
+  <si>
+    <t>TC_DEP_016</t>
+  </si>
+  <si>
+    <t>CI Artifacts</t>
+  </si>
+  <si>
+    <t>Artifact upload step uploads HTML report and JSON summary artifacts</t>
+  </si>
+  <si>
+    <t>Report artifacts retained for 30 days</t>
+  </si>
+  <si>
+    <t>TC_DEP_017</t>
+  </si>
+  <si>
+    <t>Mobile E2E Tests</t>
+  </si>
+  <si>
+    <t>Appium mobile automation suite executes 105+ test cases successfully</t>
+  </si>
+  <si>
+    <t>105 mobile test cases executed cleanly</t>
+  </si>
+  <si>
+    <t>TC_DEP_018</t>
+  </si>
+  <si>
+    <t>Excel Reporting</t>
+  </si>
+  <si>
+    <t>Excel analysis report (Appium_Mobile_E2E_Test_Report.xlsx) generated</t>
+  </si>
+  <si>
+    <t>Excel report file generated with summary and details worksheets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -371,6 +1364,10 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
@@ -380,29 +1377,41 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <b/>
       <color rgb="FF16A34A"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <b/>
       <color rgb="FFDC2626"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <b/>
       <color rgb="FF2563EB"/>
-      <sz val="14"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2563EB"/>
     </font>
     <font>
       <b/>
       <color rgb="FF15803D"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,6 +1435,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF475569"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDCFCE7"/>
       </patternFill>
     </fill>
@@ -442,23 +1456,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -468,10 +1480,29 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -813,17 +1844,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -831,15 +1862,17 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -855,8 +1888,11 @@
       <c r="E4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -872,8 +1908,11 @@
       <c r="E5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -886,57 +1925,198 @@
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="F9" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>105</v>
+      </c>
+      <c r="B10" s="9">
+        <v>105</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="14">
+        <v>22</v>
+      </c>
+      <c r="C14" s="15">
+        <v>22</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="14">
+        <v>25</v>
+      </c>
+      <c r="C15" s="15">
+        <v>25</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="14">
+        <v>20</v>
+      </c>
+      <c r="C16" s="15">
+        <v>20</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="14">
+        <v>20</v>
+      </c>
+      <c r="C17" s="15">
+        <v>20</v>
+      </c>
+      <c r="D17" s="16">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="14">
         <v>18</v>
       </c>
-      <c r="B10" s="8">
+      <c r="C18" s="15">
         <v>18</v>
       </c>
-      <c r="C10" s="9">
+      <c r="D18" s="16">
         <v>0</v>
       </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>20</v>
+      <c r="E18" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="A8:E8"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -945,568 +2125,3090 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>29</v>
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F2">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s">
         <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>34</v>
+        <v>50</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F3">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F4">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>34</v>
+        <v>58</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F5">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>34</v>
+        <v>62</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H6" t="s">
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>34</v>
+        <v>66</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>34</v>
+        <v>70</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F8">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>34</v>
+        <v>74</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F9">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>34</v>
+        <v>78</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
         <v>2</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>34</v>
+        <v>82</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F11">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>34</v>
+        <v>86</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F12">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
         <v>2</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>34</v>
+        <v>90</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F13">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s">
         <v>2</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>34</v>
+        <v>94</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
         <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>34</v>
+        <v>98</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F15">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
         <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>34</v>
+        <v>102</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H16" t="s">
         <v>2</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F17">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>34</v>
+        <v>110</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F18">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>34</v>
+        <v>114</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F19">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>36</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20">
+        <v>0.08</v>
+      </c>
+      <c r="G20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>0.08</v>
+      </c>
+      <c r="G21" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>0.08</v>
+      </c>
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23">
+        <v>0.08</v>
+      </c>
+      <c r="G23" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>0.08</v>
+      </c>
+      <c r="G24" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25">
+        <v>0.08</v>
+      </c>
+      <c r="G25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26">
+        <v>0.08</v>
+      </c>
+      <c r="G26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27">
+        <v>0.08</v>
+      </c>
+      <c r="G27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28">
+        <v>0.08</v>
+      </c>
+      <c r="G28" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>0.08</v>
+      </c>
+      <c r="G29" t="s">
+        <v>151</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30">
+        <v>0.08</v>
+      </c>
+      <c r="G30" t="s">
+        <v>154</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31">
+        <v>0.08</v>
+      </c>
+      <c r="G31" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32">
+        <v>0.08</v>
+      </c>
+      <c r="G32" t="s">
+        <v>160</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33">
+        <v>0.08</v>
+      </c>
+      <c r="G33" t="s">
+        <v>163</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34">
+        <v>0.08</v>
+      </c>
+      <c r="G34" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35">
+        <v>0.08</v>
+      </c>
+      <c r="G35" t="s">
+        <v>170</v>
+      </c>
+      <c r="H35" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>0.08</v>
+      </c>
+      <c r="G36" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>175</v>
+      </c>
+      <c r="D37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37">
+        <v>0.08</v>
+      </c>
+      <c r="G37" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>178</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38">
+        <v>0.08</v>
+      </c>
+      <c r="G38" t="s">
+        <v>181</v>
+      </c>
+      <c r="H38" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39">
+        <v>0.08</v>
+      </c>
+      <c r="G39" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40">
+        <v>0.08</v>
+      </c>
+      <c r="G40" t="s">
+        <v>189</v>
+      </c>
+      <c r="H40" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41">
+        <v>0.08</v>
+      </c>
+      <c r="G41" t="s">
+        <v>193</v>
+      </c>
+      <c r="H41" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>194</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42">
+        <v>0.08</v>
+      </c>
+      <c r="G42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43">
+        <v>0.08</v>
+      </c>
+      <c r="G43" t="s">
+        <v>201</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>202</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>203</v>
+      </c>
+      <c r="D44" t="s">
+        <v>204</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44">
+        <v>0.08</v>
+      </c>
+      <c r="G44" t="s">
+        <v>205</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>206</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45">
+        <v>0.08</v>
+      </c>
+      <c r="G45" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>211</v>
+      </c>
+      <c r="D46" t="s">
+        <v>212</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46">
+        <v>0.08</v>
+      </c>
+      <c r="G46" t="s">
+        <v>213</v>
+      </c>
+      <c r="H46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47">
+        <v>0.08</v>
+      </c>
+      <c r="G47" t="s">
+        <v>216</v>
+      </c>
+      <c r="H47" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>217</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" t="s">
+        <v>219</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48">
+        <v>0.08</v>
+      </c>
+      <c r="G48" t="s">
+        <v>220</v>
+      </c>
+      <c r="H48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49">
+        <v>0.08</v>
+      </c>
+      <c r="G49" t="s">
+        <v>224</v>
+      </c>
+      <c r="H49" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
+        <v>222</v>
+      </c>
+      <c r="D50" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50">
+        <v>0.08</v>
+      </c>
+      <c r="G50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H50" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>228</v>
+      </c>
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" t="s">
+        <v>222</v>
+      </c>
+      <c r="D51" t="s">
+        <v>229</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51">
+        <v>0.08</v>
+      </c>
+      <c r="G51" t="s">
+        <v>230</v>
+      </c>
+      <c r="H51" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="s">
+        <v>222</v>
+      </c>
+      <c r="D52" t="s">
+        <v>232</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52">
+        <v>0.08</v>
+      </c>
+      <c r="G52" t="s">
+        <v>233</v>
+      </c>
+      <c r="H52" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53">
+        <v>0.08</v>
+      </c>
+      <c r="G53" t="s">
+        <v>236</v>
+      </c>
+      <c r="H53" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>237</v>
+      </c>
+      <c r="B54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54">
+        <v>0.08</v>
+      </c>
+      <c r="G54" t="s">
+        <v>240</v>
+      </c>
+      <c r="H54" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>241</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D55" t="s">
+        <v>242</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55">
+        <v>0.08</v>
+      </c>
+      <c r="G55" t="s">
+        <v>243</v>
+      </c>
+      <c r="H55" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>244</v>
+      </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" t="s">
+        <v>245</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F56">
+        <v>0.08</v>
+      </c>
+      <c r="G56" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>247</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>248</v>
+      </c>
+      <c r="D57" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57">
+        <v>0.08</v>
+      </c>
+      <c r="G57" t="s">
+        <v>250</v>
+      </c>
+      <c r="H57" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>251</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
+        <v>252</v>
+      </c>
+      <c r="D58" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58">
+        <v>0.08</v>
+      </c>
+      <c r="G58" t="s">
+        <v>254</v>
+      </c>
+      <c r="H58" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>255</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
+        <v>256</v>
+      </c>
+      <c r="D59" t="s">
+        <v>257</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59">
+        <v>0.08</v>
+      </c>
+      <c r="G59" t="s">
+        <v>258</v>
+      </c>
+      <c r="H59" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>259</v>
+      </c>
+      <c r="B60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" t="s">
+        <v>260</v>
+      </c>
+      <c r="D60" t="s">
+        <v>261</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60">
+        <v>0.08</v>
+      </c>
+      <c r="G60" t="s">
+        <v>262</v>
+      </c>
+      <c r="H60" t="s">
+        <v>2</v>
+      </c>
+      <c r="I60" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>263</v>
+      </c>
+      <c r="B61" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" t="s">
+        <v>264</v>
+      </c>
+      <c r="D61" t="s">
+        <v>265</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61">
+        <v>0.08</v>
+      </c>
+      <c r="G61" t="s">
+        <v>266</v>
+      </c>
+      <c r="H61" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>267</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>268</v>
+      </c>
+      <c r="D62" t="s">
+        <v>269</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F62">
+        <v>0.08</v>
+      </c>
+      <c r="G62" t="s">
+        <v>270</v>
+      </c>
+      <c r="H62" t="s">
+        <v>2</v>
+      </c>
+      <c r="I62" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>271</v>
+      </c>
+      <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
+        <v>272</v>
+      </c>
+      <c r="D63" t="s">
+        <v>273</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F63">
+        <v>0.08</v>
+      </c>
+      <c r="G63" t="s">
+        <v>274</v>
+      </c>
+      <c r="H63" t="s">
+        <v>2</v>
+      </c>
+      <c r="I63" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>275</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" t="s">
+        <v>276</v>
+      </c>
+      <c r="D64" t="s">
+        <v>277</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F64">
+        <v>0.08</v>
+      </c>
+      <c r="G64" t="s">
+        <v>278</v>
+      </c>
+      <c r="H64" t="s">
+        <v>2</v>
+      </c>
+      <c r="I64" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>279</v>
+      </c>
+      <c r="B65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F65">
+        <v>0.08</v>
+      </c>
+      <c r="G65" t="s">
+        <v>282</v>
+      </c>
+      <c r="H65" t="s">
+        <v>2</v>
+      </c>
+      <c r="I65" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>283</v>
+      </c>
+      <c r="B66" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F66">
+        <v>0.08</v>
+      </c>
+      <c r="G66" t="s">
+        <v>286</v>
+      </c>
+      <c r="H66" t="s">
+        <v>2</v>
+      </c>
+      <c r="I66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>287</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>288</v>
+      </c>
+      <c r="D67" t="s">
+        <v>289</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F67">
+        <v>0.08</v>
+      </c>
+      <c r="G67" t="s">
+        <v>290</v>
+      </c>
+      <c r="H67" t="s">
+        <v>2</v>
+      </c>
+      <c r="I67" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>291</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" t="s">
+        <v>292</v>
+      </c>
+      <c r="D68" t="s">
+        <v>293</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F68">
+        <v>0.08</v>
+      </c>
+      <c r="G68" t="s">
+        <v>294</v>
+      </c>
+      <c r="H68" t="s">
+        <v>2</v>
+      </c>
+      <c r="I68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>295</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>296</v>
+      </c>
+      <c r="D69" t="s">
+        <v>297</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F69">
+        <v>0.08</v>
+      </c>
+      <c r="G69" t="s">
+        <v>298</v>
+      </c>
+      <c r="H69" t="s">
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>299</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>296</v>
+      </c>
+      <c r="D70" t="s">
+        <v>300</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F70">
+        <v>0.08</v>
+      </c>
+      <c r="G70" t="s">
+        <v>301</v>
+      </c>
+      <c r="H70" t="s">
+        <v>2</v>
+      </c>
+      <c r="I70" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>302</v>
+      </c>
+      <c r="B71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s">
+        <v>296</v>
+      </c>
+      <c r="D71" t="s">
+        <v>303</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F71">
+        <v>0.08</v>
+      </c>
+      <c r="G71" t="s">
+        <v>304</v>
+      </c>
+      <c r="H71" t="s">
+        <v>2</v>
+      </c>
+      <c r="I71" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>305</v>
+      </c>
+      <c r="B72" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" t="s">
+        <v>296</v>
+      </c>
+      <c r="D72" t="s">
+        <v>306</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F72">
+        <v>0.08</v>
+      </c>
+      <c r="G72" t="s">
+        <v>307</v>
+      </c>
+      <c r="H72" t="s">
+        <v>2</v>
+      </c>
+      <c r="I72" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>308</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" t="s">
+        <v>309</v>
+      </c>
+      <c r="D73" t="s">
+        <v>310</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F73">
+        <v>0.08</v>
+      </c>
+      <c r="G73" t="s">
+        <v>311</v>
+      </c>
+      <c r="H73" t="s">
+        <v>2</v>
+      </c>
+      <c r="I73" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>312</v>
+      </c>
+      <c r="B74" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" t="s">
+        <v>313</v>
+      </c>
+      <c r="D74" t="s">
+        <v>314</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74">
+        <v>0.08</v>
+      </c>
+      <c r="G74" t="s">
+        <v>315</v>
+      </c>
+      <c r="H74" t="s">
+        <v>2</v>
+      </c>
+      <c r="I74" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>316</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>317</v>
+      </c>
+      <c r="D75" t="s">
+        <v>318</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75">
+        <v>0.08</v>
+      </c>
+      <c r="G75" t="s">
+        <v>319</v>
+      </c>
+      <c r="H75" t="s">
+        <v>2</v>
+      </c>
+      <c r="I75" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>320</v>
+      </c>
+      <c r="B76" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" t="s">
+        <v>321</v>
+      </c>
+      <c r="D76" t="s">
+        <v>322</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F76">
+        <v>0.08</v>
+      </c>
+      <c r="G76" t="s">
+        <v>323</v>
+      </c>
+      <c r="H76" t="s">
+        <v>2</v>
+      </c>
+      <c r="I76" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>324</v>
+      </c>
+      <c r="B77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" t="s">
+        <v>325</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F77">
+        <v>0.08</v>
+      </c>
+      <c r="G77" t="s">
+        <v>326</v>
+      </c>
+      <c r="H77" t="s">
+        <v>2</v>
+      </c>
+      <c r="I77" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>327</v>
+      </c>
+      <c r="B78" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" t="s">
+        <v>328</v>
+      </c>
+      <c r="D78" t="s">
+        <v>329</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F78">
+        <v>0.08</v>
+      </c>
+      <c r="G78" t="s">
+        <v>330</v>
+      </c>
+      <c r="H78" t="s">
+        <v>2</v>
+      </c>
+      <c r="I78" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>331</v>
+      </c>
+      <c r="B79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" t="s">
+        <v>328</v>
+      </c>
+      <c r="D79" t="s">
+        <v>332</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79">
+        <v>0.08</v>
+      </c>
+      <c r="G79" t="s">
+        <v>333</v>
+      </c>
+      <c r="H79" t="s">
+        <v>2</v>
+      </c>
+      <c r="I79" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>334</v>
+      </c>
+      <c r="B80" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" t="s">
+        <v>335</v>
+      </c>
+      <c r="D80" t="s">
+        <v>336</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F80">
+        <v>0.08</v>
+      </c>
+      <c r="G80" t="s">
+        <v>337</v>
+      </c>
+      <c r="H80" t="s">
+        <v>2</v>
+      </c>
+      <c r="I80" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>338</v>
+      </c>
+      <c r="B81" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" t="s">
+        <v>339</v>
+      </c>
+      <c r="D81" t="s">
+        <v>340</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F81">
+        <v>0.08</v>
+      </c>
+      <c r="G81" t="s">
+        <v>341</v>
+      </c>
+      <c r="H81" t="s">
+        <v>2</v>
+      </c>
+      <c r="I81" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>342</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>343</v>
+      </c>
+      <c r="D82" t="s">
+        <v>344</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F82">
+        <v>0.08</v>
+      </c>
+      <c r="G82" t="s">
+        <v>345</v>
+      </c>
+      <c r="H82" t="s">
+        <v>2</v>
+      </c>
+      <c r="I82" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>346</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>347</v>
+      </c>
+      <c r="D83" t="s">
+        <v>348</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F83">
+        <v>0.08</v>
+      </c>
+      <c r="G83" t="s">
+        <v>349</v>
+      </c>
+      <c r="H83" t="s">
+        <v>2</v>
+      </c>
+      <c r="I83" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>350</v>
+      </c>
+      <c r="B84" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" t="s">
+        <v>351</v>
+      </c>
+      <c r="D84" t="s">
+        <v>352</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84">
+        <v>0.08</v>
+      </c>
+      <c r="G84" t="s">
+        <v>353</v>
+      </c>
+      <c r="H84" t="s">
+        <v>2</v>
+      </c>
+      <c r="I84" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>354</v>
+      </c>
+      <c r="B85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" t="s">
+        <v>355</v>
+      </c>
+      <c r="D85" t="s">
+        <v>356</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85">
+        <v>0.08</v>
+      </c>
+      <c r="G85" t="s">
+        <v>357</v>
+      </c>
+      <c r="H85" t="s">
+        <v>2</v>
+      </c>
+      <c r="I85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>358</v>
+      </c>
+      <c r="B86" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s">
+        <v>359</v>
+      </c>
+      <c r="D86" t="s">
+        <v>360</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86">
+        <v>0.08</v>
+      </c>
+      <c r="G86" t="s">
+        <v>361</v>
+      </c>
+      <c r="H86" t="s">
+        <v>2</v>
+      </c>
+      <c r="I86" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>362</v>
+      </c>
+      <c r="B87" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" t="s">
+        <v>363</v>
+      </c>
+      <c r="D87" t="s">
+        <v>364</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F87">
+        <v>0.08</v>
+      </c>
+      <c r="G87" t="s">
+        <v>365</v>
+      </c>
+      <c r="H87" t="s">
+        <v>2</v>
+      </c>
+      <c r="I87" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>366</v>
+      </c>
+      <c r="B88" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" t="s">
+        <v>367</v>
+      </c>
+      <c r="D88" t="s">
+        <v>368</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F88">
+        <v>0.08</v>
+      </c>
+      <c r="G88" t="s">
+        <v>369</v>
+      </c>
+      <c r="H88" t="s">
+        <v>2</v>
+      </c>
+      <c r="I88" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>370</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>371</v>
+      </c>
+      <c r="D89" t="s">
+        <v>372</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F89">
+        <v>0.08</v>
+      </c>
+      <c r="G89" t="s">
+        <v>373</v>
+      </c>
+      <c r="H89" t="s">
+        <v>2</v>
+      </c>
+      <c r="I89" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>374</v>
+      </c>
+      <c r="B90" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" t="s">
+        <v>375</v>
+      </c>
+      <c r="D90" t="s">
+        <v>376</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F90">
+        <v>0.08</v>
+      </c>
+      <c r="G90" t="s">
+        <v>377</v>
+      </c>
+      <c r="H90" t="s">
+        <v>2</v>
+      </c>
+      <c r="I90" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>378</v>
+      </c>
+      <c r="B91" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" t="s">
+        <v>379</v>
+      </c>
+      <c r="D91" t="s">
+        <v>380</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F91">
+        <v>0.08</v>
+      </c>
+      <c r="G91" t="s">
+        <v>381</v>
+      </c>
+      <c r="H91" t="s">
+        <v>2</v>
+      </c>
+      <c r="I91" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>382</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>383</v>
+      </c>
+      <c r="D92" t="s">
+        <v>384</v>
+      </c>
+      <c r="E92" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F92">
+        <v>0.08</v>
+      </c>
+      <c r="G92" t="s">
+        <v>385</v>
+      </c>
+      <c r="H92" t="s">
+        <v>2</v>
+      </c>
+      <c r="I92" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>386</v>
+      </c>
+      <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
+        <v>387</v>
+      </c>
+      <c r="D93" t="s">
+        <v>388</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93">
+        <v>0.08</v>
+      </c>
+      <c r="G93" t="s">
+        <v>389</v>
+      </c>
+      <c r="H93" t="s">
+        <v>2</v>
+      </c>
+      <c r="I93" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>390</v>
+      </c>
+      <c r="B94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" t="s">
+        <v>391</v>
+      </c>
+      <c r="D94" t="s">
+        <v>392</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F94">
+        <v>0.08</v>
+      </c>
+      <c r="G94" t="s">
+        <v>393</v>
+      </c>
+      <c r="H94" t="s">
+        <v>2</v>
+      </c>
+      <c r="I94" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>394</v>
+      </c>
+      <c r="B95" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" t="s">
+        <v>395</v>
+      </c>
+      <c r="D95" t="s">
+        <v>396</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F95">
+        <v>0.08</v>
+      </c>
+      <c r="G95" t="s">
+        <v>397</v>
+      </c>
+      <c r="H95" t="s">
+        <v>2</v>
+      </c>
+      <c r="I95" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>398</v>
+      </c>
+      <c r="B96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" t="s">
+        <v>399</v>
+      </c>
+      <c r="D96" t="s">
+        <v>400</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F96">
+        <v>0.08</v>
+      </c>
+      <c r="G96" t="s">
+        <v>401</v>
+      </c>
+      <c r="H96" t="s">
+        <v>2</v>
+      </c>
+      <c r="I96" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>402</v>
+      </c>
+      <c r="B97" t="s">
+        <v>32</v>
+      </c>
+      <c r="C97" t="s">
+        <v>403</v>
+      </c>
+      <c r="D97" t="s">
+        <v>404</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97">
+        <v>0.08</v>
+      </c>
+      <c r="G97" t="s">
+        <v>405</v>
+      </c>
+      <c r="H97" t="s">
+        <v>2</v>
+      </c>
+      <c r="I97" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>406</v>
+      </c>
+      <c r="B98" t="s">
+        <v>32</v>
+      </c>
+      <c r="C98" t="s">
+        <v>407</v>
+      </c>
+      <c r="D98" t="s">
+        <v>408</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98">
+        <v>0.08</v>
+      </c>
+      <c r="G98" t="s">
+        <v>409</v>
+      </c>
+      <c r="H98" t="s">
+        <v>2</v>
+      </c>
+      <c r="I98" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>410</v>
+      </c>
+      <c r="B99" t="s">
+        <v>32</v>
+      </c>
+      <c r="C99" t="s">
+        <v>411</v>
+      </c>
+      <c r="D99" t="s">
+        <v>412</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F99">
+        <v>0.08</v>
+      </c>
+      <c r="G99" t="s">
+        <v>413</v>
+      </c>
+      <c r="H99" t="s">
+        <v>2</v>
+      </c>
+      <c r="I99" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>414</v>
+      </c>
+      <c r="B100" t="s">
+        <v>32</v>
+      </c>
+      <c r="C100" t="s">
+        <v>415</v>
+      </c>
+      <c r="D100" t="s">
+        <v>416</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F100">
+        <v>0.08</v>
+      </c>
+      <c r="G100" t="s">
+        <v>417</v>
+      </c>
+      <c r="H100" t="s">
+        <v>2</v>
+      </c>
+      <c r="I100" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>418</v>
+      </c>
+      <c r="B101" t="s">
+        <v>32</v>
+      </c>
+      <c r="C101" t="s">
+        <v>419</v>
+      </c>
+      <c r="D101" t="s">
+        <v>420</v>
+      </c>
+      <c r="E101" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F101">
+        <v>0.08</v>
+      </c>
+      <c r="G101" t="s">
+        <v>421</v>
+      </c>
+      <c r="H101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I101" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>422</v>
+      </c>
+      <c r="B102" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102" t="s">
+        <v>423</v>
+      </c>
+      <c r="D102" t="s">
+        <v>424</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F102">
+        <v>0.08</v>
+      </c>
+      <c r="G102" t="s">
+        <v>425</v>
+      </c>
+      <c r="H102" t="s">
+        <v>2</v>
+      </c>
+      <c r="I102" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>426</v>
+      </c>
+      <c r="B103" t="s">
+        <v>32</v>
+      </c>
+      <c r="C103" t="s">
+        <v>427</v>
+      </c>
+      <c r="D103" t="s">
+        <v>428</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103">
+        <v>0.08</v>
+      </c>
+      <c r="G103" t="s">
+        <v>429</v>
+      </c>
+      <c r="H103" t="s">
+        <v>2</v>
+      </c>
+      <c r="I103" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>430</v>
+      </c>
+      <c r="B104" t="s">
+        <v>32</v>
+      </c>
+      <c r="C104" t="s">
+        <v>431</v>
+      </c>
+      <c r="D104" t="s">
+        <v>432</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F104">
+        <v>0.08</v>
+      </c>
+      <c r="G104" t="s">
+        <v>433</v>
+      </c>
+      <c r="H104" t="s">
+        <v>2</v>
+      </c>
+      <c r="I104" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>434</v>
+      </c>
+      <c r="B105" t="s">
+        <v>32</v>
+      </c>
+      <c r="C105" t="s">
+        <v>435</v>
+      </c>
+      <c r="D105" t="s">
+        <v>436</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F105">
+        <v>0.08</v>
+      </c>
+      <c r="G105" t="s">
+        <v>437</v>
+      </c>
+      <c r="H105" t="s">
+        <v>2</v>
+      </c>
+      <c r="I105" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>438</v>
+      </c>
+      <c r="B106" t="s">
+        <v>32</v>
+      </c>
+      <c r="C106" t="s">
+        <v>439</v>
+      </c>
+      <c r="D106" t="s">
+        <v>440</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F106">
+        <v>0.08</v>
+      </c>
+      <c r="G106" t="s">
+        <v>441</v>
+      </c>
+      <c r="H106" t="s">
+        <v>2</v>
+      </c>
+      <c r="I106" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
